--- a/docs/downloads/经营分_鲁东省区__青岛西片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁东省区__青岛西片区_2026-10-18.xlsx
@@ -966,14 +966,14 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>稳房源,提质量,附加分,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -1001,7 +1001,7 @@
         <v>30</v>
       </c>
       <c r="S5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T5" t="n">
         <v>20</v>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1321,7 +1321,7 @@
         <v>90</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>95</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H31" t="n">
